--- a/output/pdf_financials_xlsx/MCCP.P.xlsx
+++ b/output/pdf_financials_xlsx/MCCP.P.xlsx
@@ -469,15 +469,11 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -486,15 +482,11 @@
           <t xml:space="preserve">  Cost of Goods Sold</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -503,15 +495,11 @@
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -520,15 +508,11 @@
           <t xml:space="preserve">  Selling, General, &amp; Admin. Expense</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -537,15 +521,11 @@
           <t xml:space="preserve">  Research &amp; Development</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -554,15 +534,11 @@
           <t xml:space="preserve">  Other Operating Expense</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -571,15 +547,11 @@
           <t xml:space="preserve">  Total Operating Expense</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -588,15 +560,11 @@
           <t>Operating Income</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -605,15 +573,11 @@
           <t xml:space="preserve">    Interest Income</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -622,15 +586,11 @@
           <t xml:space="preserve">    Interest Expense</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -639,15 +599,11 @@
           <t xml:space="preserve">  Net Interest Income</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -656,15 +612,11 @@
           <t xml:space="preserve">  Other Income (Expense)</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -673,15 +625,11 @@
           <t>Pretax Income</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B16" s="3" t="n">
+        <v>-0.315998</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>-0.315998</v>
       </c>
     </row>
     <row r="17">
@@ -690,15 +638,11 @@
           <t xml:space="preserve">  Tax Provision</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -741,15 +685,11 @@
           <t xml:space="preserve">    Net Income (Continuing Operations)</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B20" s="3" t="n">
+        <v>-0.315998</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>-0.315998</v>
       </c>
     </row>
     <row r="21">
@@ -758,15 +698,11 @@
           <t xml:space="preserve">    Net Income (Discontinued Operations)</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -775,15 +711,11 @@
           <t xml:space="preserve">  Other Income (Minority Interest)</t>
         </is>
       </c>
-      <c r="B22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -792,15 +724,11 @@
           <t>Net Income</t>
         </is>
       </c>
-      <c r="B23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B23" s="3" t="n">
+        <v>-0.315998</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>-0.315998</v>
       </c>
     </row>
     <row r="24">
@@ -822,15 +750,11 @@
           <t>EPS (Diluted)</t>
         </is>
       </c>
-      <c r="B25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B25" s="3" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>0.04</v>
       </c>
     </row>
     <row r="26">
@@ -839,15 +763,11 @@
           <t>Shares Outstanding (Diluted Average)</t>
         </is>
       </c>
-      <c r="B26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B26" s="3" t="n">
+        <v>-1.436355</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>-7.89995</v>
       </c>
     </row>
     <row r="27">
@@ -856,15 +776,11 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B27" s="3" t="n">
+        <v>-0.315998</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>-0.315998</v>
       </c>
     </row>
     <row r="28">
@@ -873,15 +789,11 @@
           <t xml:space="preserve">  Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -890,15 +802,11 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B29" s="3" t="n">
+        <v>-0.315998</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>-0.315998</v>
       </c>
     </row>
     <row r="30">
@@ -924,15 +832,11 @@
           <t>Tax Rate %</t>
         </is>
       </c>
-      <c r="B31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -965,15 +869,11 @@
           <t xml:space="preserve">    Cash and Cash Equivalents</t>
         </is>
       </c>
-      <c r="B34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -982,15 +882,11 @@
           <t xml:space="preserve">    Marketable Securities</t>
         </is>
       </c>
-      <c r="B35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -999,15 +895,11 @@
           <t xml:space="preserve">  Cash, Cash Equivalents, Marketable Securities</t>
         </is>
       </c>
-      <c r="B36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -1016,15 +908,11 @@
           <t xml:space="preserve">    Accounts Receivable</t>
         </is>
       </c>
-      <c r="B37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -1033,15 +921,11 @@
           <t xml:space="preserve">    Notes Receivable</t>
         </is>
       </c>
-      <c r="B38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -1050,15 +934,11 @@
           <t xml:space="preserve">    Loans Receivable</t>
         </is>
       </c>
-      <c r="B39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -1067,10 +947,8 @@
           <t xml:space="preserve">    Other Current Receivables</t>
         </is>
       </c>
-      <c r="B40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B40" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C40" s="3" t="n">
         <v>0.002527</v>
@@ -1082,15 +960,11 @@
           <t xml:space="preserve">  Total Receivables</t>
         </is>
       </c>
-      <c r="B41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>0.002527</v>
       </c>
     </row>
     <row r="42">
@@ -1099,15 +973,11 @@
           <t xml:space="preserve">    Inventories, Raw Materials &amp; Components</t>
         </is>
       </c>
-      <c r="B42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -1116,15 +986,11 @@
           <t xml:space="preserve">    Inventories, Work In Process</t>
         </is>
       </c>
-      <c r="B43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -1133,15 +999,11 @@
           <t xml:space="preserve">    Inventories, Inventories Adjustments</t>
         </is>
       </c>
-      <c r="B44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -1150,15 +1012,11 @@
           <t xml:space="preserve">    Inventories, Finished Goods</t>
         </is>
       </c>
-      <c r="B45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -1167,15 +1025,11 @@
           <t xml:space="preserve">    Inventories, Other</t>
         </is>
       </c>
-      <c r="B46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -1184,15 +1038,11 @@
           <t xml:space="preserve">  Total Inventories</t>
         </is>
       </c>
-      <c r="B47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -1201,15 +1051,11 @@
           <t xml:space="preserve">  Other Current Assets</t>
         </is>
       </c>
-      <c r="B48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B48" s="3" t="n">
+        <v>0.556187</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>0.484351</v>
       </c>
     </row>
     <row r="49">
@@ -1218,15 +1064,11 @@
           <t xml:space="preserve">  Total Current Assets</t>
         </is>
       </c>
-      <c r="B49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B49" s="3" t="n">
+        <v>0.556187</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>0.486878</v>
       </c>
     </row>
     <row r="50">
@@ -1235,15 +1077,11 @@
           <t xml:space="preserve">  Investments And Advances</t>
         </is>
       </c>
-      <c r="B50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -1252,15 +1090,11 @@
           <t xml:space="preserve">      Land And Improvements</t>
         </is>
       </c>
-      <c r="B51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -1269,15 +1103,11 @@
           <t xml:space="preserve">      Buildings And Improvements</t>
         </is>
       </c>
-      <c r="B52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -1286,15 +1116,11 @@
           <t xml:space="preserve">      Machinery, Furniture, Equipment</t>
         </is>
       </c>
-      <c r="B53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -1303,15 +1129,11 @@
           <t xml:space="preserve">      Construction In Progress</t>
         </is>
       </c>
-      <c r="B54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -1337,15 +1159,11 @@
           <t xml:space="preserve">    Gross Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="B56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -1354,15 +1172,11 @@
           <t xml:space="preserve">    Accumulated Depreciation</t>
         </is>
       </c>
-      <c r="B57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -1371,15 +1185,11 @@
           <t xml:space="preserve">  Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="B58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -1388,15 +1198,11 @@
           <t xml:space="preserve">  Intangible Assets</t>
         </is>
       </c>
-      <c r="B59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -1405,15 +1211,11 @@
           <t xml:space="preserve">    Goodwill</t>
         </is>
       </c>
-      <c r="B60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -1422,15 +1224,11 @@
           <t xml:space="preserve">  Other Long Term Assets</t>
         </is>
       </c>
-      <c r="B61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -1473,15 +1271,11 @@
           <t xml:space="preserve">    Accounts Payable</t>
         </is>
       </c>
-      <c r="B64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -1490,15 +1284,11 @@
           <t xml:space="preserve">    Total Tax Payable</t>
         </is>
       </c>
-      <c r="B65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -1507,15 +1297,11 @@
           <t xml:space="preserve">    Other Current Payables</t>
         </is>
       </c>
-      <c r="B66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -1524,15 +1310,11 @@
           <t xml:space="preserve">    Current Accrued Expense</t>
         </is>
       </c>
-      <c r="B67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -1554,15 +1336,11 @@
           <t xml:space="preserve">    Short-Term Debt</t>
         </is>
       </c>
-      <c r="B69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -1571,15 +1349,11 @@
           <t xml:space="preserve">    Short-Term Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -1588,15 +1362,11 @@
           <t xml:space="preserve">  Short-Term Debt &amp; Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -1605,15 +1375,11 @@
           <t xml:space="preserve">    Current Deferred Revenue</t>
         </is>
       </c>
-      <c r="B72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -1622,15 +1388,11 @@
           <t xml:space="preserve">    Current Deferred Taxes Liabilities</t>
         </is>
       </c>
-      <c r="B73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -1639,15 +1401,11 @@
           <t xml:space="preserve">  Deferred Tax And Revenue</t>
         </is>
       </c>
-      <c r="B74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -1656,15 +1414,11 @@
           <t xml:space="preserve">  Other Current Liabilities</t>
         </is>
       </c>
-      <c r="B75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -1690,15 +1444,11 @@
           <t xml:space="preserve">    Long-Term Debt</t>
         </is>
       </c>
-      <c r="B77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -1707,15 +1457,11 @@
           <t xml:space="preserve">    Long-Term Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -1724,15 +1470,11 @@
           <t xml:space="preserve">  Long-Term Debt &amp; Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -1758,15 +1500,11 @@
           <t xml:space="preserve">  Pension And Retirement Benefit</t>
         </is>
       </c>
-      <c r="B81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C81" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -1775,15 +1513,11 @@
           <t xml:space="preserve">    NonCurrent Deferred Revenue</t>
         </is>
       </c>
-      <c r="B82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C82" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -1792,15 +1526,11 @@
           <t xml:space="preserve">  NonCurrent Deferred Liabilities</t>
         </is>
       </c>
-      <c r="B83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C83" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -1809,15 +1539,11 @@
           <t xml:space="preserve">  NonCurrent Deferred Income Tax</t>
         </is>
       </c>
-      <c r="B84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C84" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -1826,15 +1552,11 @@
           <t xml:space="preserve">  Other Long-Term Liabilities</t>
         </is>
       </c>
-      <c r="B85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C85" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -1877,15 +1599,11 @@
           <t xml:space="preserve">  Common Stock</t>
         </is>
       </c>
-      <c r="B88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B88" s="3" t="n">
+        <v>0.730809</v>
+      </c>
+      <c r="C88" s="3" t="n">
+        <v>0.730809</v>
       </c>
     </row>
     <row r="89">
@@ -1894,15 +1612,11 @@
           <t xml:space="preserve">  Preferred Stock</t>
         </is>
       </c>
-      <c r="B89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C89" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -1924,15 +1638,11 @@
           <t xml:space="preserve">  Accumulated other comprehensive income (loss)</t>
         </is>
       </c>
-      <c r="B91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C91" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -1954,15 +1664,11 @@
           <t xml:space="preserve">  Treasury Stock</t>
         </is>
       </c>
-      <c r="B93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C93" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -1971,15 +1677,11 @@
           <t xml:space="preserve">  Total Stockholders Equity</t>
         </is>
       </c>
-      <c r="B94" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C94" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B94" s="3" t="n">
+        <v>0.53187</v>
+      </c>
+      <c r="C94" s="3" t="n">
+        <v>0.474489</v>
       </c>
     </row>
     <row r="95">
@@ -1988,15 +1690,11 @@
           <t xml:space="preserve">  Minority Interest</t>
         </is>
       </c>
-      <c r="B95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C95" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -2005,15 +1703,11 @@
           <t>Total Equity</t>
         </is>
       </c>
-      <c r="B96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B96" s="3" t="n">
+        <v>0.53187</v>
+      </c>
+      <c r="C96" s="3" t="n">
+        <v>0.474489</v>
       </c>
     </row>
     <row r="97">
@@ -2046,15 +1740,11 @@
           <t xml:space="preserve">  Net Income From Continuing Operations</t>
         </is>
       </c>
-      <c r="B99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B99" s="3" t="n">
+        <v>-0.315998</v>
+      </c>
+      <c r="C99" s="3" t="n">
+        <v>-0.057381</v>
       </c>
     </row>
     <row r="100">
@@ -2063,15 +1753,11 @@
           <t xml:space="preserve">  Cash Flow Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C100" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -2080,10 +1766,8 @@
           <t xml:space="preserve">    Change In Receivables</t>
         </is>
       </c>
-      <c r="B101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B101" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C101" s="3" t="n">
         <v>-0.002527</v>
@@ -2095,15 +1779,11 @@
           <t xml:space="preserve">    Change In Inventory</t>
         </is>
       </c>
-      <c r="B102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C102" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -2112,15 +1792,11 @@
           <t xml:space="preserve">    Change In Prepaid Assets</t>
         </is>
       </c>
-      <c r="B103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C103" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -2142,15 +1818,11 @@
           <t xml:space="preserve">    Change In Other Working Capital</t>
         </is>
       </c>
-      <c r="B105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C105" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -2159,15 +1831,11 @@
           <t xml:space="preserve">  Change In Working Capital</t>
         </is>
       </c>
-      <c r="B106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B106" s="3" t="n">
+        <v>0.024317</v>
+      </c>
+      <c r="C106" s="3" t="n">
+        <v>-0.014455</v>
       </c>
     </row>
     <row r="107">
@@ -2179,10 +1847,8 @@
       <c r="B107" s="3" t="n">
         <v>0.077871</v>
       </c>
-      <c r="C107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C107" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -2191,15 +1857,11 @@
           <t xml:space="preserve">  Asset Impairment Charge</t>
         </is>
       </c>
-      <c r="B108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C108" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -2208,15 +1870,11 @@
           <t xml:space="preserve">  Cash from Discontinued Operating Activities</t>
         </is>
       </c>
-      <c r="B109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C109" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -2225,15 +1883,11 @@
           <t xml:space="preserve">  Cash Flow from Others</t>
         </is>
       </c>
-      <c r="B110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C110" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -2242,15 +1896,11 @@
           <t xml:space="preserve">  Purchase Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C111" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -2259,15 +1909,11 @@
           <t xml:space="preserve">  Sale Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C112" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -2276,15 +1922,11 @@
           <t xml:space="preserve">  Purchase Of Business</t>
         </is>
       </c>
-      <c r="B113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C113" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -2293,15 +1935,11 @@
           <t xml:space="preserve">  Purchase Of Investment</t>
         </is>
       </c>
-      <c r="B114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C114" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -2310,15 +1948,11 @@
           <t xml:space="preserve">  Sale Of Investment</t>
         </is>
       </c>
-      <c r="B115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C115" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -2327,15 +1961,11 @@
           <t xml:space="preserve">  Net Intangibles Purchase And Sale</t>
         </is>
       </c>
-      <c r="B116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C116" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -2344,15 +1974,11 @@
           <t xml:space="preserve">  Cash From Discontinued Investing Activities</t>
         </is>
       </c>
-      <c r="B117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C117" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -2361,15 +1987,11 @@
           <t xml:space="preserve">  Cash From Other Investing Activities</t>
         </is>
       </c>
-      <c r="B118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C118" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -2378,10 +2000,8 @@
           <t>Cash Flow from Investing</t>
         </is>
       </c>
-      <c r="B119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B119" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C119" s="1" t="inlineStr">
         <is>
@@ -2395,15 +2015,11 @@
           <t xml:space="preserve">  Issuance of Stock</t>
         </is>
       </c>
-      <c r="B120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C120" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -2412,15 +2028,11 @@
           <t xml:space="preserve">  Repurchase of Stock</t>
         </is>
       </c>
-      <c r="B121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C121" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -2429,15 +2041,11 @@
           <t xml:space="preserve">  Net Issuance of Preferred Stock</t>
         </is>
       </c>
-      <c r="B122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C122" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -2446,15 +2054,11 @@
           <t xml:space="preserve">    Issuance of Debt</t>
         </is>
       </c>
-      <c r="B123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C123" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -2463,15 +2067,11 @@
           <t xml:space="preserve">    Payments of Debt</t>
         </is>
       </c>
-      <c r="B124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C124" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -2480,15 +2080,11 @@
           <t xml:space="preserve">  Net Issuance of Debt</t>
         </is>
       </c>
-      <c r="B125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C125" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -2497,15 +2093,11 @@
           <t xml:space="preserve">  Cash Flow for Dividends</t>
         </is>
       </c>
-      <c r="B126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C126" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -2531,15 +2123,11 @@
           <t xml:space="preserve">  Other Financing</t>
         </is>
       </c>
-      <c r="B128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C128" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -2563,10 +2151,8 @@
           <t xml:space="preserve">  Beginning Cash Position</t>
         </is>
       </c>
-      <c r="B130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B130" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C130" s="3" t="n">
         <v>0.556187</v>
@@ -2578,15 +2164,11 @@
           <t xml:space="preserve">    Effect of Exchange Rate Changes</t>
         </is>
       </c>
-      <c r="B131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C131" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -2621,15 +2203,11 @@
           <t>Capital Expenditure</t>
         </is>
       </c>
-      <c r="B134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C134" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -2638,15 +2216,11 @@
           <t>Free Cash Flow</t>
         </is>
       </c>
-      <c r="B135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B135" s="3" t="n">
+        <v>-0.21381</v>
+      </c>
+      <c r="C135" s="3" t="n">
+        <v>-0.071836</v>
       </c>
     </row>
   </sheetData>
@@ -2660,7 +2234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2772,10 +2346,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>$</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Current assets total</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>CurrentAssets</t>
+        </is>
+      </c>
       <c r="E4" s="5" t="n">
         <v>0.556187</v>
       </c>
@@ -2935,7 +2513,11 @@
           <t>Shareholders’ equity total</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>StockholdersEquity</t>
+        </is>
+      </c>
       <c r="E10" s="5" t="n">
         <v>0.53187</v>
       </c>
@@ -2946,25 +2528,29 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Shareholders’ equity</t>
+          <t>Cash flows from operating activities</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>$</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Net loss for the period $</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E11" s="5" t="n">
-        <v>0.556187</v>
+        <v>-0.315998</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.486878</v>
+        <v>-0.057381</v>
       </c>
     </row>
     <row r="12">
@@ -2980,15 +2566,21 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Net loss for the period $</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Share based compensation</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E12" s="5" t="n">
-        <v>-0.315998</v>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>-0.057381</v>
+        <v>0.077871</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -2999,26 +2591,26 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cash flows from operating activities</t>
+          <t>Change in non-cash working capital</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Share based compensation</t>
+          <t>Accounts Receivable</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="n">
-        <v>0.077871</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-0.002527</v>
       </c>
     </row>
     <row r="14">
@@ -3034,21 +2626,19 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Accounts Receivable</t>
+          <t>Accounts payable and accrued liabilities</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ChangeInReceivables</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.024317</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>-0.002527</v>
+        <v>-0.011928</v>
       </c>
     </row>
     <row r="15">
@@ -3064,19 +2654,19 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities</t>
+          <t>Net cash used in operating activities</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
+          <t>OperatingCashFlow</t>
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>0.024317</v>
+        <v>-0.21381</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>-0.011928</v>
+        <v>-0.071836</v>
       </c>
     </row>
     <row r="16">
@@ -3087,24 +2677,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Change in non-cash working capital</t>
+          <t>Cash flows from financing activities</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Net cash used in operating activities</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>OperatingCashFlow</t>
-        </is>
-      </c>
+          <t>Issuance of share capital, net of issuance costs</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" s="5" t="n">
-        <v>-0.21381</v>
-      </c>
-      <c r="F16" s="5" t="n">
-        <v>-0.071836</v>
+        <v>0.769997</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -3120,10 +2708,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Issuance of share capital, net of issuance costs</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Net cash from financing activities</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
       <c r="E17" s="5" t="n">
         <v>0.769997</v>
       </c>
@@ -3146,21 +2738,19 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Net cash from financing activities</t>
+          <t>Change in cash</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>FinancingCashFlow</t>
+          <t>ChangesInCash</t>
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>0.769997</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.556187</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>-0.071836</v>
       </c>
     </row>
     <row r="19">
@@ -3176,19 +2766,21 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Change in cash</t>
+          <t>Cash, beginning of period</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="n">
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="n">
         <v>0.556187</v>
-      </c>
-      <c r="F19" s="5" t="n">
-        <v>-0.071836</v>
       </c>
     </row>
     <row r="20">
@@ -3204,49 +2796,47 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cash, beginning of period</t>
+          <t>Cash, end of period $</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>0.556187</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>0.556187</v>
+        <v>0.484351</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>income_statement</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Cash flows from financing activities</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Cash, end of period $</t>
+          <t>General and administrative expense (note 7) $</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
+          <t>GeneralAndAdministrativeExpense</t>
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>0.556187</v>
+        <v>0.238127</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>0.484351</v>
+        <v>0.057381</v>
       </c>
     </row>
     <row r="22">
@@ -3262,19 +2852,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>General and administrative expense (note 7) $</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>Share based compensation</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" s="5" t="n">
-        <v>0.238127</v>
-      </c>
-      <c r="F22" s="5" t="n">
-        <v>0.057381</v>
+        <v>0.077871</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -3290,17 +2878,19 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Share based compensation</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
+          <t>Net loss and comprehensive loss for the period $</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E23" s="5" t="n">
-        <v>0.077871</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.315998</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>0.057381</v>
       </c>
     </row>
     <row r="24">
@@ -3311,20 +2901,24 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Loss per share</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the period $</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
+          <t>Basic and diluted $</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E24" s="5" t="n">
-        <v>0.315998</v>
+        <v>2.2e-07</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>0.057381</v>
+        <v>4e-08</v>
       </c>
     </row>
     <row r="25">
@@ -3335,24 +2929,20 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Loss per share</t>
+          <t>Weighted average number of common shares outstanding</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Basic and diluted $</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Basic and diluted</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" s="5" t="n">
-        <v>2.2e-07</v>
+        <v>1.443155</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>4e-08</v>
+        <v>1.443155</v>
       </c>
     </row>
     <row r="26">
@@ -3363,20 +2953,22 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
+          <t>Contributed shareholders’</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Basic and diluted</t>
+          <t>Issue of common shares $ 900,000 $ - $ - $</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" s="5" t="n">
-        <v>1.443155</v>
-      </c>
-      <c r="F26" s="5" t="n">
-        <v>1.443155</v>
+        <v>0.9</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="27">
@@ -3392,12 +2984,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Issue of common shares $ 900,000 $ - $ - $</t>
+          <t>Share issuance costs (130,003) - -</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" s="5" t="n">
-        <v>0.9</v>
+        <v>-0.130003</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3418,12 +3010,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Share issuance costs (130,003) - -</t>
+          <t>Warrants issued (39,188) - 39,188</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
-      <c r="E28" s="5" t="n">
-        <v>-0.130003</v>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3444,14 +3038,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Warrants issued (39,188) - 39,188</t>
+          <t>Share based compensation - 77,871 -</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E29" s="5" t="n">
+        <v>0.077871</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3472,17 +3064,19 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Share based compensation - 77,871 -</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
+          <t>Net loss for the period - - -</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E30" s="5" t="n">
-        <v>0.077871</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.315998</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>-0.315998</v>
       </c>
     </row>
     <row r="31">
@@ -3498,12 +3092,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Net loss for the period - - -</t>
+          <t>December 31, 2021 $ 730,809 $ 77,871 $ 39,188 $</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" s="5" t="n">
-        <v>-0.315998</v>
+        <v>0.53187</v>
       </c>
       <c r="F31" s="5" t="n">
         <v>-0.315998</v>
@@ -3522,38 +3116,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>December 31, 2021 $ 730,809 $ 77,871 $ 39,188 $</t>
+          <t>December 31, 2022 $ 730,809 $ 77,871 $ 39,188 $</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" s="5" t="n">
-        <v>0.53187</v>
+        <v>0.474489</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>-0.315998</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Contributed shareholders’</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>December 31, 2022 $ 730,809 $ 77,871 $ 39,188 $</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" s="5" t="n">
-        <v>0.474489</v>
-      </c>
-      <c r="F33" s="5" t="n">
         <v>-0.373379</v>
       </c>
     </row>

--- a/output/pdf_financials_xlsx/MCCP.P.xlsx
+++ b/output/pdf_financials_xlsx/MCCP.P.xlsx
@@ -431,6 +431,11 @@
   </sheetPr>
   <dimension ref="A1:C135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">

--- a/output/pdf_financials_xlsx/MCCP.P.xlsx
+++ b/output/pdf_financials_xlsx/MCCP.P.xlsx
@@ -592,10 +592,10 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="14">
@@ -644,10 +644,10 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="18">
@@ -2239,7 +2239,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3132,6 +3132,188 @@
         <v>-0.373379</v>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Contributed                                shareholders’</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Issue of common shares $ 900,000 $ - $ - $</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" s="5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Contributed                                shareholders’</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Share issuance costs (130,003) - -</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" s="5" t="n">
+        <v>-0.130003</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Contributed                                shareholders’</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Warrants issued (39,188) - 39,188</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Contributed                                shareholders’</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Share based compensation - 77,871 -</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" s="5" t="n">
+        <v>0.077871</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Contributed                                shareholders’</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Net loss for the period - - -</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="n">
+        <v>-0.315998</v>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>-0.315998</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Contributed                                shareholders’</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>December 31, 2021 $ 730,809 $ 77,871 $ 39,188 $</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" s="5" t="n">
+        <v>0.53187</v>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>-0.315998</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Contributed                                shareholders’</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>December 31, 2022 $ 730,809 $ 77,871 $ 39,188 $</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" s="5" t="n">
+        <v>0.474489</v>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v>-0.373379</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/pdf_financials_xlsx/MCCP.P.xlsx
+++ b/output/pdf_financials_xlsx/MCCP.P.xlsx
@@ -2892,10 +2892,10 @@
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>0.315998</v>
+        <v>-0.315998</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>0.057381</v>
+        <v>-0.057381</v>
       </c>
     </row>
     <row r="24">

--- a/output/pdf_financials_xlsx/MCCP.P.xlsx
+++ b/output/pdf_financials_xlsx/MCCP.P.xlsx
@@ -875,10 +875,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.556187</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.484351</v>
       </c>
     </row>
     <row r="35">
@@ -901,10 +901,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.556187</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.484351</v>
       </c>
     </row>
     <row r="37">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.556187</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.484351</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
